--- a/sources/3B_Manha_2_Bimestre.xlsx
+++ b/sources/3B_Manha_2_Bimestre.xlsx
@@ -61,7 +61,7 @@
     <x:t>Conselho Segundo Bimestre</x:t>
   </x:si>
   <x:si>
-    <x:t>246</x:t>
+    <x:t>356</x:t>
   </x:si>
   <x:si>
     <x:t>0 (Soma de todas as eletivas)</x:t>
@@ -162,274 +162,274 @@
     <x:t>Ativo</x:t>
   </x:si>
   <x:si>
+    <x:t>7</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>74%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>80%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANDREY SILVA SOUZA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>95%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>96%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BEATRIZ REINALDO DE ALMEIDA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>86%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>90%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIANCA NASHYLAY GALLO FERREIRA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>85%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>87%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EMILLYN NOEMI ARAUJO COSTA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>88%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ESTER COSTA CAETANO DA SILVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>41</x:t>
+  </x:si>
+  <x:si>
+    <x:t>93%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>101%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FELIPE MATHEUS DA SILVA LIMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>94%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>102%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GABRIEL VITOR CASTRO DE ANDRADE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Não Comparecimento</x:t>
+  </x:si>
+  <x:si>
     <x:t>-</x:t>
   </x:si>
   <x:si>
-    <x:t>9</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4</x:t>
-  </x:si>
-  <x:si>
-    <x:t>6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>8</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12</x:t>
+    <x:t>100%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GIULLIA POSSAM GREGORIO DOS SANTOS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GUSTAVO LEAL DA SILVA SA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>111</x:t>
+  </x:si>
+  <x:si>
+    <x:t>92%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>108%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IZABELLA MAISA NOGUEIRA DE MENEZES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>97%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JOAO VITOR PEREIRA MESQUITA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>16</x:t>
+  </x:si>
+  <x:si>
+    <x:t>78%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JORDI SILVA MOURA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JOSE FRANCISCO MEIRA ABREU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>89%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GABRIELY SANTIAGO RODRIGUES MARINHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>83%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KAUA ALVES DOS SANTOS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LUCAS NEVES VIEIRA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>77%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LUCCAS NAZARIO FREIRE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARIA EDUARDA MOREIRA ALVES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARIA LUIZA NASCIMENTO DE OLIVEIRA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARIANA BARRETO DE SOUZA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARIANE GUIMARAES BORGES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MAYARA ROSETTI SILVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MILLENI DOS SANTOS DIAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13</x:t>
+  </x:si>
+  <x:si>
+    <x:t>68%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOISÉS DINIZ DO NASCIMENTO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15</x:t>
+  </x:si>
+  <x:si>
+    <x:t>70%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>66%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NICOLLY CAROLINE TONON MONTAGNOLI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RYAN GUEDES DE BRITO FRANCISCO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Remanejamento</x:t>
+  </x:si>
+  <x:si>
+    <x:t>81%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SABRINA LUZ COELHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>99%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SARAH LUZ COELHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>STHELLA ANDRÉ ALMEIDA</x:t>
   </x:si>
   <x:si>
     <x:t>76%</x:t>
   </x:si>
   <x:si>
-    <x:t>82%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANDREY SILVA SOUZA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>7</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1</x:t>
+    <x:t>79%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>URIEL DA SILVEIRA MARQUES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VICTORIA BATISTA PEREIRA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VINICIUS MARINHO SILVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VITOR FERREIRA DIAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VITORIA MANUELLA OLIVEIRA DE SOUSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VITORIA MARIA DE JESUS TORRES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YASMIN VIEIRA DE ABREU</x:t>
   </x:si>
   <x:si>
     <x:t>98%</x:t>
   </x:si>
   <x:si>
-    <x:t>BEATRIZ REINALDO DE ALMEIDA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>89%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>92%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIANCA NASHYLAY GALLO FERREIRA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>87%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EMILLYN NOEMI ARAUJO COSTA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>85%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ESTER COSTA CAETANO DA SILVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>41</x:t>
-  </x:si>
-  <x:si>
-    <x:t>93%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>102%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FELIPE MATHEUS DA SILVA LIMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>104%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GABRIEL VITOR CASTRO DE ANDRADE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Não Comparecimento</x:t>
-  </x:si>
-  <x:si>
-    <x:t>100%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>70%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GIULLIA POSSAM GREGORIO DOS SANTOS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>95%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>96%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GUSTAVO LEAL DA SILVA SA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>111</x:t>
-  </x:si>
-  <x:si>
-    <x:t>112%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IZABELLA MAISA NOGUEIRA DE MENEZES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>97%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>JOAO VITOR PEREIRA MESQUITA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>16</x:t>
-  </x:si>
-  <x:si>
-    <x:t>77%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>JORDI SILVA MOURA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>JOSE FRANCISCO MEIRA ABREU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>90%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>88%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GABRIELY SANTIAGO RODRIGUES MARINHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KAUA ALVES DOS SANTOS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>91%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LUCAS NEVES VIEIRA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>79%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LUCCAS NAZARIO FREIRE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MARIA EDUARDA MOREIRA ALVES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MARIA LUIZA NASCIMENTO DE OLIVEIRA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MARIANA BARRETO DE SOUZA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MARIANE GUIMARAES BORGES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MAYARA ROSETTI SILVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>84%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MILLENI DOS SANTOS DIAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13</x:t>
-  </x:si>
-  <x:si>
-    <x:t>86%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOISÉS DINIZ DO NASCIMENTO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15</x:t>
-  </x:si>
-  <x:si>
-    <x:t>67%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>64%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NICOLLY CAROLINE TONON MONTAGNOLI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RYAN GUEDES DE BRITO FRANCISCO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Remanejamento</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SABRINA LUZ COELHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>99%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SARAH LUZ COELHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>STHELLA ANDRÉ ALMEIDA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>81%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>URIEL DA SILVEIRA MARQUES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VICTORIA BATISTA PEREIRA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VINICIUS MARINHO SILVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VITOR FERREIRA DIAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VITORIA MANUELLA OLIVEIRA DE SOUSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>75%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VITORIA MARIA DE JESUS TORRES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>94%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YASMIN VIEIRA DE ABREU</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve"> </x:t>
   </x:si>
   <x:si>
-    <x:t>Aulas Dadas: 0</x:t>
+    <x:t>Aulas Dadas: 30</x:t>
   </x:si>
   <x:si>
     <x:t>Aulas Dadas: 33</x:t>
@@ -442,6 +442,9 @@
   </x:si>
   <x:si>
     <x:t>Aulas Dadas: 54</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Aulas Dadas: 50</x:t>
   </x:si>
   <x:si>
     <x:t>Aulas Dadas: 31</x:t>
@@ -1335,94 +1338,94 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="E13" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="F13" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="G13" s="12">
         <x:v>1</x:v>
       </x:c>
       <x:c r="H13" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="I13" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="J13" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="K13" s="12">
         <x:v>1</x:v>
       </x:c>
       <x:c r="L13" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="M13" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="N13" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="O13" s="12">
         <x:v>1</x:v>
       </x:c>
       <x:c r="P13" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="Q13" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="R13" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="S13" s="12">
         <x:v>1</x:v>
       </x:c>
       <x:c r="T13" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="U13" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="V13" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="W13" s="12">
         <x:v>1</x:v>
       </x:c>
       <x:c r="X13" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="Y13" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="Z13" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AA13" s="12">
         <x:v>1</x:v>
       </x:c>
       <x:c r="AB13" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AC13" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AD13" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AE13" s="12">
         <x:v>1</x:v>
       </x:c>
       <x:c r="AF13" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AG13" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AH13" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AI13" s="12">
         <x:v>1</x:v>
@@ -1431,51 +1434,51 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="AK13" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AL13" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AM13" s="12">
         <x:v>1</x:v>
       </x:c>
       <x:c r="AN13" s="12" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="AO13" s="12" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="AO13" s="12" t="s">
-        <x:v>55</x:v>
-      </x:c>
       <x:c r="AP13" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AQ13" s="12">
         <x:v>1</x:v>
       </x:c>
       <x:c r="AR13" s="12" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="AS13" s="12" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="AT13" s="12" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="AS13" s="12" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="AT13" s="12" t="s">
-        <x:v>55</x:v>
-      </x:c>
       <x:c r="AU13" s="12">
-        <x:v>59</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="AV13" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AW13" s="12">
-        <x:v>104</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="AX13" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:50">
       <x:c r="A14" s="11" t="s">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B14" s="12" t="s">
         <x:v>44</x:v>
@@ -1484,25 +1487,25 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="D14" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E14" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="F14" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="G14" s="12">
         <x:v>2</x:v>
       </x:c>
       <x:c r="H14" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="I14" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="J14" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="K14" s="12">
         <x:v>2</x:v>
@@ -1511,123 +1514,123 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="M14" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="N14" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="O14" s="12">
         <x:v>2</x:v>
       </x:c>
       <x:c r="P14" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="Q14" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="R14" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="S14" s="12">
         <x:v>2</x:v>
       </x:c>
       <x:c r="T14" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="U14" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="V14" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="W14" s="12">
         <x:v>2</x:v>
       </x:c>
       <x:c r="X14" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="Y14" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="Z14" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AA14" s="12">
         <x:v>2</x:v>
       </x:c>
       <x:c r="AB14" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AC14" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AD14" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AE14" s="12">
         <x:v>2</x:v>
       </x:c>
       <x:c r="AF14" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AG14" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="AH14" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AI14" s="12">
         <x:v>2</x:v>
       </x:c>
       <x:c r="AJ14" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AK14" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AL14" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AM14" s="12">
         <x:v>2</x:v>
       </x:c>
       <x:c r="AN14" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AO14" s="12" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="AP14" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AQ14" s="12">
         <x:v>2</x:v>
       </x:c>
       <x:c r="AR14" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AS14" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AT14" s="12" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="AU14" s="12">
-        <x:v>5</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="AV14" s="12" t="s">
         <x:v>63</x:v>
       </x:c>
       <x:c r="AW14" s="12">
-        <x:v>13</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="AX14" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:50">
       <x:c r="A15" s="11" t="s">
-        <x:v>64</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B15" s="12" t="s">
         <x:v>44</x:v>
@@ -1639,147 +1642,147 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="E15" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="F15" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="G15" s="12">
         <x:v>3</x:v>
       </x:c>
       <x:c r="H15" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="I15" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="J15" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="K15" s="12">
         <x:v>3</x:v>
       </x:c>
       <x:c r="L15" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="M15" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="N15" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="O15" s="12">
         <x:v>3</x:v>
       </x:c>
       <x:c r="P15" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="Q15" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="R15" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="S15" s="12">
         <x:v>3</x:v>
       </x:c>
       <x:c r="T15" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="U15" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="V15" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="W15" s="12">
         <x:v>3</x:v>
       </x:c>
       <x:c r="X15" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="Y15" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="Z15" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AA15" s="12">
         <x:v>3</x:v>
       </x:c>
       <x:c r="AB15" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AC15" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AD15" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AE15" s="12">
         <x:v>3</x:v>
       </x:c>
       <x:c r="AF15" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AG15" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AH15" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AI15" s="12">
         <x:v>3</x:v>
       </x:c>
       <x:c r="AJ15" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AK15" s="12" t="s">
         <x:v>45</x:v>
       </x:c>
       <x:c r="AL15" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AM15" s="12">
         <x:v>3</x:v>
       </x:c>
       <x:c r="AN15" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AO15" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AP15" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AQ15" s="12">
         <x:v>3</x:v>
       </x:c>
       <x:c r="AR15" s="12" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="AS15" s="12" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="AT15" s="12" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="AS15" s="12" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="AT15" s="12" t="s">
-        <x:v>55</x:v>
-      </x:c>
       <x:c r="AU15" s="12">
-        <x:v>26</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AV15" s="12" t="s">
-        <x:v>65</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="AW15" s="12">
-        <x:v>44</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="AX15" s="12" t="s">
-        <x:v>66</x:v>
+        <x:v>67</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:50">
       <x:c r="A16" s="11" t="s">
-        <x:v>67</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B16" s="12" t="s">
         <x:v>44</x:v>
@@ -1788,25 +1791,25 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="D16" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="E16" s="12" t="s">
         <x:v>45</x:v>
       </x:c>
       <x:c r="F16" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="G16" s="12">
         <x:v>4</x:v>
       </x:c>
       <x:c r="H16" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="I16" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="J16" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="K16" s="12">
         <x:v>4</x:v>
@@ -1815,123 +1818,123 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="M16" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="N16" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="O16" s="12">
         <x:v>4</x:v>
       </x:c>
       <x:c r="P16" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="Q16" s="12" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="R16" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="S16" s="12">
         <x:v>4</x:v>
       </x:c>
       <x:c r="T16" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="U16" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="V16" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="W16" s="12">
         <x:v>4</x:v>
       </x:c>
       <x:c r="X16" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="Y16" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="Z16" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AA16" s="12">
         <x:v>4</x:v>
       </x:c>
       <x:c r="AB16" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AC16" s="12" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="AD16" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AE16" s="12">
         <x:v>4</x:v>
       </x:c>
       <x:c r="AF16" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AG16" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AH16" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AI16" s="12">
         <x:v>4</x:v>
       </x:c>
       <x:c r="AJ16" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AK16" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AL16" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AM16" s="12">
         <x:v>4</x:v>
       </x:c>
       <x:c r="AN16" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AO16" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AP16" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AQ16" s="12">
         <x:v>4</x:v>
       </x:c>
       <x:c r="AR16" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AS16" s="12" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="AT16" s="12" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="AT16" s="12" t="s">
-        <x:v>53</x:v>
-      </x:c>
       <x:c r="AU16" s="12">
-        <x:v>32</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AV16" s="12" t="s">
-        <x:v>68</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="AW16" s="12">
-        <x:v>65</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="AX16" s="12" t="s">
-        <x:v>65</x:v>
+        <x:v>70</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:50">
       <x:c r="A17" s="11" t="s">
-        <x:v>69</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B17" s="12" t="s">
         <x:v>44</x:v>
@@ -1940,97 +1943,97 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="D17" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E17" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="F17" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="G17" s="12">
         <x:v>5</x:v>
       </x:c>
       <x:c r="H17" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="I17" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="J17" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="K17" s="12">
         <x:v>5</x:v>
       </x:c>
       <x:c r="L17" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="M17" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="N17" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="O17" s="12">
         <x:v>5</x:v>
       </x:c>
       <x:c r="P17" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="Q17" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="R17" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="S17" s="12">
         <x:v>5</x:v>
       </x:c>
       <x:c r="T17" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="U17" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="V17" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="W17" s="12">
         <x:v>5</x:v>
       </x:c>
       <x:c r="X17" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="Y17" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="Z17" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AA17" s="12">
         <x:v>5</x:v>
       </x:c>
       <x:c r="AB17" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AC17" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AD17" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AE17" s="12">
         <x:v>5</x:v>
       </x:c>
       <x:c r="AF17" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AG17" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AH17" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AI17" s="12">
         <x:v>5</x:v>
@@ -2039,51 +2042,51 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="AK17" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AL17" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AM17" s="12">
         <x:v>5</x:v>
       </x:c>
       <x:c r="AN17" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AO17" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AP17" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AQ17" s="12">
         <x:v>5</x:v>
       </x:c>
       <x:c r="AR17" s="12" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="AS17" s="12" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="AT17" s="12" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="AS17" s="12" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="AT17" s="12" t="s">
-        <x:v>55</x:v>
-      </x:c>
       <x:c r="AU17" s="12">
-        <x:v>37</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AV17" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="AW17" s="12">
-        <x:v>63</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="AX17" s="12" t="s">
-        <x:v>65</x:v>
+        <x:v>72</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:50">
       <x:c r="A18" s="11" t="s">
-        <x:v>71</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B18" s="12" t="s">
         <x:v>44</x:v>
@@ -2092,25 +2095,25 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="D18" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E18" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="F18" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="G18" s="12">
         <x:v>6</x:v>
       </x:c>
       <x:c r="H18" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="I18" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="J18" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="K18" s="12">
         <x:v>6</x:v>
@@ -2119,123 +2122,123 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="M18" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="N18" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="O18" s="12">
         <x:v>6</x:v>
       </x:c>
       <x:c r="P18" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="Q18" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="R18" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="S18" s="12">
         <x:v>6</x:v>
       </x:c>
       <x:c r="T18" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="U18" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="V18" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="W18" s="12">
         <x:v>6</x:v>
       </x:c>
       <x:c r="X18" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="Y18" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="Z18" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AA18" s="12">
         <x:v>6</x:v>
       </x:c>
       <x:c r="AB18" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AC18" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="AD18" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AE18" s="12">
         <x:v>6</x:v>
       </x:c>
       <x:c r="AF18" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AG18" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AH18" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AI18" s="12">
         <x:v>6</x:v>
       </x:c>
       <x:c r="AJ18" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AK18" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AL18" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AM18" s="12">
         <x:v>6</x:v>
       </x:c>
       <x:c r="AN18" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AO18" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AP18" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AQ18" s="12">
         <x:v>6</x:v>
       </x:c>
       <x:c r="AR18" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AS18" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AT18" s="12" t="s">
-        <x:v>72</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="AU18" s="12">
-        <x:v>18</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="AV18" s="12" t="s">
-        <x:v>73</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="AW18" s="12">
-        <x:v>-14</x:v>
+        <x:v>-7</x:v>
       </x:c>
       <x:c r="AX18" s="12" t="s">
-        <x:v>74</x:v>
+        <x:v>76</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:50">
       <x:c r="A19" s="11" t="s">
-        <x:v>75</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B19" s="12" t="s">
         <x:v>44</x:v>
@@ -2247,22 +2250,22 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="E19" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="F19" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="G19" s="12">
         <x:v>7</x:v>
       </x:c>
       <x:c r="H19" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="I19" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="J19" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="K19" s="12">
         <x:v>7</x:v>
@@ -2271,275 +2274,275 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="M19" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="N19" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="O19" s="12">
         <x:v>7</x:v>
       </x:c>
       <x:c r="P19" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="Q19" s="12" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="R19" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="S19" s="12">
         <x:v>7</x:v>
       </x:c>
       <x:c r="T19" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="U19" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="V19" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="W19" s="12">
         <x:v>7</x:v>
       </x:c>
       <x:c r="X19" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="Y19" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="Z19" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AA19" s="12">
         <x:v>7</x:v>
       </x:c>
       <x:c r="AB19" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AC19" s="12" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="AD19" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AE19" s="12">
         <x:v>7</x:v>
       </x:c>
       <x:c r="AF19" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AG19" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AH19" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AI19" s="12">
         <x:v>7</x:v>
       </x:c>
       <x:c r="AJ19" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AK19" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AL19" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AM19" s="12">
         <x:v>7</x:v>
       </x:c>
       <x:c r="AN19" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AO19" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AP19" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AQ19" s="12">
         <x:v>7</x:v>
       </x:c>
       <x:c r="AR19" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AS19" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AT19" s="12" t="s">
-        <x:v>72</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="AU19" s="12">
-        <x:v>17</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="AV19" s="12" t="s">
-        <x:v>73</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="AW19" s="12">
-        <x:v>-21</x:v>
+        <x:v>-16</x:v>
       </x:c>
       <x:c r="AX19" s="12" t="s">
-        <x:v>76</x:v>
+        <x:v>79</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:50">
       <x:c r="A20" s="11" t="s">
-        <x:v>77</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B20" s="12" t="s">
-        <x:v>78</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C20" s="12">
         <x:v>8</x:v>
       </x:c>
       <x:c r="D20" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="E20" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="F20" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="G20" s="12">
         <x:v>8</x:v>
       </x:c>
       <x:c r="H20" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="I20" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="J20" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="K20" s="12">
         <x:v>8</x:v>
       </x:c>
       <x:c r="L20" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="M20" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="N20" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="O20" s="12">
         <x:v>8</x:v>
       </x:c>
       <x:c r="P20" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="Q20" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="R20" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="S20" s="12">
         <x:v>8</x:v>
       </x:c>
       <x:c r="T20" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="U20" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="V20" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="W20" s="12">
         <x:v>8</x:v>
       </x:c>
       <x:c r="X20" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="Y20" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="Z20" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AA20" s="12">
         <x:v>8</x:v>
       </x:c>
       <x:c r="AB20" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="AC20" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AD20" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AE20" s="12">
         <x:v>8</x:v>
       </x:c>
       <x:c r="AF20" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="AG20" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AH20" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AI20" s="12">
         <x:v>8</x:v>
       </x:c>
       <x:c r="AJ20" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="AK20" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AL20" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AM20" s="12">
         <x:v>8</x:v>
       </x:c>
       <x:c r="AN20" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="AO20" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AP20" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AQ20" s="12">
         <x:v>8</x:v>
       </x:c>
       <x:c r="AR20" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="AS20" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AT20" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AU20" s="12">
         <x:v>0</x:v>
       </x:c>
       <x:c r="AV20" s="12" t="s">
-        <x:v>79</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="AW20" s="12">
         <x:v>174</x:v>
       </x:c>
       <x:c r="AX20" s="12" t="s">
-        <x:v>80</x:v>
+        <x:v>57</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:50">
       <x:c r="A21" s="11" t="s">
-        <x:v>81</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B21" s="12" t="s">
         <x:v>44</x:v>
@@ -2548,25 +2551,25 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D21" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E21" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="F21" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="G21" s="12">
         <x:v>9</x:v>
       </x:c>
       <x:c r="H21" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="I21" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="J21" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="K21" s="12">
         <x:v>9</x:v>
@@ -2575,123 +2578,123 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="M21" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="N21" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="O21" s="12">
         <x:v>9</x:v>
       </x:c>
       <x:c r="P21" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="Q21" s="12" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="R21" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="S21" s="12">
         <x:v>9</x:v>
       </x:c>
       <x:c r="T21" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="U21" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="V21" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="W21" s="12">
         <x:v>9</x:v>
       </x:c>
       <x:c r="X21" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="Y21" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="Z21" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AA21" s="12">
         <x:v>9</x:v>
       </x:c>
       <x:c r="AB21" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AC21" s="12" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="AD21" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AE21" s="12">
         <x:v>9</x:v>
       </x:c>
       <x:c r="AF21" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AG21" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AH21" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AI21" s="12">
         <x:v>9</x:v>
       </x:c>
       <x:c r="AJ21" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AK21" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AL21" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AM21" s="12">
         <x:v>9</x:v>
       </x:c>
       <x:c r="AN21" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AO21" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AP21" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AQ21" s="12">
         <x:v>9</x:v>
       </x:c>
       <x:c r="AR21" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AS21" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AT21" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AU21" s="12">
-        <x:v>12</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="AV21" s="12" t="s">
-        <x:v>82</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AW21" s="12">
-        <x:v>22</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="AX21" s="12" t="s">
-        <x:v>83</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:50">
       <x:c r="A22" s="11" t="s">
-        <x:v>84</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B22" s="12" t="s">
         <x:v>44</x:v>
@@ -2700,150 +2703,150 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="D22" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E22" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="F22" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="G22" s="12">
         <x:v>10</x:v>
       </x:c>
       <x:c r="H22" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="I22" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="J22" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="K22" s="12">
         <x:v>10</x:v>
       </x:c>
       <x:c r="L22" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="M22" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="N22" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="O22" s="12">
         <x:v>10</x:v>
       </x:c>
       <x:c r="P22" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="Q22" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="R22" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="S22" s="12">
         <x:v>10</x:v>
       </x:c>
       <x:c r="T22" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="U22" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="V22" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="W22" s="12">
         <x:v>10</x:v>
       </x:c>
       <x:c r="X22" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="Y22" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="Z22" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AA22" s="12">
         <x:v>10</x:v>
       </x:c>
       <x:c r="AB22" s="12" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="AC22" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="AC22" s="12" t="s">
-        <x:v>47</x:v>
-      </x:c>
       <x:c r="AD22" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AE22" s="12">
         <x:v>10</x:v>
       </x:c>
       <x:c r="AF22" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AG22" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AH22" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AI22" s="12">
         <x:v>10</x:v>
       </x:c>
       <x:c r="AJ22" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AK22" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="AL22" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AM22" s="12">
         <x:v>10</x:v>
       </x:c>
       <x:c r="AN22" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AO22" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="AP22" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AQ22" s="12">
         <x:v>10</x:v>
       </x:c>
       <x:c r="AR22" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AS22" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AT22" s="12" t="s">
-        <x:v>85</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="AU22" s="12">
-        <x:v>16</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="AV22" s="12" t="s">
-        <x:v>73</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="AW22" s="12">
-        <x:v>-69</x:v>
+        <x:v>-57</x:v>
       </x:c>
       <x:c r="AX22" s="12" t="s">
-        <x:v>86</x:v>
+        <x:v>88</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:50">
       <x:c r="A23" s="11" t="s">
-        <x:v>87</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B23" s="12" t="s">
         <x:v>44</x:v>
@@ -2855,22 +2858,22 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="E23" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="F23" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="G23" s="12">
         <x:v>11</x:v>
       </x:c>
       <x:c r="H23" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="I23" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="J23" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="K23" s="12">
         <x:v>11</x:v>
@@ -2879,70 +2882,70 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="M23" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="N23" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="O23" s="12">
         <x:v>11</x:v>
       </x:c>
       <x:c r="P23" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="Q23" s="12" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="R23" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="S23" s="12">
         <x:v>11</x:v>
       </x:c>
       <x:c r="T23" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="U23" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="V23" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="W23" s="12">
         <x:v>11</x:v>
       </x:c>
       <x:c r="X23" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="Y23" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="Z23" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AA23" s="12">
         <x:v>11</x:v>
       </x:c>
       <x:c r="AB23" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AC23" s="12" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="AD23" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AE23" s="12">
         <x:v>11</x:v>
       </x:c>
       <x:c r="AF23" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AG23" s="12" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="AH23" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AI23" s="12">
         <x:v>11</x:v>
@@ -2951,51 +2954,51 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="AK23" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AL23" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AM23" s="12">
         <x:v>11</x:v>
       </x:c>
       <x:c r="AN23" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AO23" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AP23" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AQ23" s="12">
         <x:v>11</x:v>
       </x:c>
       <x:c r="AR23" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AS23" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AT23" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AU23" s="12">
-        <x:v>16</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="AV23" s="12" t="s">
-        <x:v>73</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AW23" s="12">
-        <x:v>18</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="AX23" s="12" t="s">
-        <x:v>88</x:v>
+        <x:v>90</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:50">
       <x:c r="A24" s="11" t="s">
-        <x:v>89</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B24" s="12" t="s">
         <x:v>44</x:v>
@@ -3004,97 +3007,97 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="D24" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E24" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="F24" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="G24" s="12">
         <x:v>12</x:v>
       </x:c>
       <x:c r="H24" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="I24" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="J24" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="K24" s="12">
         <x:v>12</x:v>
       </x:c>
       <x:c r="L24" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="M24" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="N24" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="O24" s="12">
         <x:v>12</x:v>
       </x:c>
       <x:c r="P24" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="Q24" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="R24" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="S24" s="12">
         <x:v>12</x:v>
       </x:c>
       <x:c r="T24" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="U24" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="V24" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="W24" s="12">
         <x:v>12</x:v>
       </x:c>
       <x:c r="X24" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="Y24" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="Z24" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AA24" s="12">
         <x:v>12</x:v>
       </x:c>
       <x:c r="AB24" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AC24" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AD24" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AE24" s="12">
         <x:v>12</x:v>
       </x:c>
       <x:c r="AF24" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="AG24" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AH24" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AI24" s="12">
         <x:v>12</x:v>
@@ -3103,51 +3106,51 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="AK24" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AL24" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AM24" s="12">
         <x:v>12</x:v>
       </x:c>
       <x:c r="AN24" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AO24" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AP24" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AQ24" s="12">
         <x:v>12</x:v>
       </x:c>
       <x:c r="AR24" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AS24" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AT24" s="12" t="s">
-        <x:v>90</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="AU24" s="12">
-        <x:v>57</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="AV24" s="12" t="s">
-        <x:v>91</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="AW24" s="12">
-        <x:v>131</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="AX24" s="12" t="s">
-        <x:v>91</x:v>
+        <x:v>93</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:50">
       <x:c r="A25" s="11" t="s">
-        <x:v>92</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B25" s="12" t="s">
         <x:v>44</x:v>
@@ -3156,150 +3159,150 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="D25" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="E25" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="F25" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="G25" s="12">
         <x:v>13</x:v>
       </x:c>
       <x:c r="H25" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="I25" s="12" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="J25" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="K25" s="12">
         <x:v>13</x:v>
       </x:c>
       <x:c r="L25" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="M25" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="N25" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="O25" s="12">
         <x:v>13</x:v>
       </x:c>
       <x:c r="P25" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="Q25" s="12" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="R25" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="S25" s="12">
         <x:v>13</x:v>
       </x:c>
       <x:c r="T25" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="U25" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="V25" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="W25" s="12">
         <x:v>13</x:v>
       </x:c>
       <x:c r="X25" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="Y25" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="Z25" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AA25" s="12">
         <x:v>13</x:v>
       </x:c>
       <x:c r="AB25" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AC25" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="AD25" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AE25" s="12">
         <x:v>13</x:v>
       </x:c>
       <x:c r="AF25" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AG25" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AH25" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AI25" s="12">
         <x:v>13</x:v>
       </x:c>
       <x:c r="AJ25" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AK25" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AL25" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AM25" s="12">
         <x:v>13</x:v>
       </x:c>
       <x:c r="AN25" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AO25" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AP25" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AQ25" s="12">
         <x:v>13</x:v>
       </x:c>
       <x:c r="AR25" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AS25" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AT25" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AU25" s="12">
-        <x:v>13</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="AV25" s="12" t="s">
-        <x:v>82</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="AW25" s="12">
-        <x:v>28</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="AX25" s="12" t="s">
-        <x:v>82</x:v>
+        <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:50">
       <x:c r="A26" s="11" t="s">
-        <x:v>93</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B26" s="12" t="s">
         <x:v>44</x:v>
@@ -3308,150 +3311,150 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="D26" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="E26" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="F26" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="G26" s="12">
         <x:v>14</x:v>
       </x:c>
       <x:c r="H26" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="I26" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="J26" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="K26" s="12">
         <x:v>14</x:v>
       </x:c>
       <x:c r="L26" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="M26" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="N26" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="O26" s="12">
         <x:v>14</x:v>
       </x:c>
       <x:c r="P26" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="Q26" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="R26" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="S26" s="12">
         <x:v>14</x:v>
       </x:c>
       <x:c r="T26" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="U26" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="V26" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="W26" s="12">
         <x:v>14</x:v>
       </x:c>
       <x:c r="X26" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="Y26" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="Z26" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AA26" s="12">
         <x:v>14</x:v>
       </x:c>
       <x:c r="AB26" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AC26" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AD26" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AE26" s="12">
         <x:v>14</x:v>
       </x:c>
       <x:c r="AF26" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="AG26" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AH26" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AI26" s="12">
         <x:v>14</x:v>
       </x:c>
       <x:c r="AJ26" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AK26" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AL26" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AM26" s="12">
         <x:v>14</x:v>
       </x:c>
       <x:c r="AN26" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AO26" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="AP26" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AQ26" s="12">
         <x:v>14</x:v>
       </x:c>
       <x:c r="AR26" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AS26" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AT26" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AU26" s="12">
-        <x:v>25</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="AV26" s="12" t="s">
-        <x:v>94</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="AW26" s="12">
-        <x:v>69</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="AX26" s="12" t="s">
-        <x:v>95</x:v>
+        <x:v>72</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:50">
       <x:c r="A27" s="11" t="s">
-        <x:v>96</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B27" s="12" t="s">
         <x:v>44</x:v>
@@ -3460,97 +3463,97 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="D27" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E27" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="F27" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="G27" s="12">
         <x:v>15</x:v>
       </x:c>
       <x:c r="H27" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="I27" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="J27" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="K27" s="12">
         <x:v>15</x:v>
       </x:c>
       <x:c r="L27" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="M27" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="N27" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="O27" s="12">
         <x:v>15</x:v>
       </x:c>
       <x:c r="P27" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="Q27" s="12" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="R27" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="S27" s="12">
         <x:v>15</x:v>
       </x:c>
       <x:c r="T27" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="U27" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="V27" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="W27" s="12">
         <x:v>15</x:v>
       </x:c>
       <x:c r="X27" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="Y27" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="Z27" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AA27" s="12">
         <x:v>15</x:v>
       </x:c>
       <x:c r="AB27" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AC27" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AD27" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AE27" s="12">
         <x:v>15</x:v>
       </x:c>
       <x:c r="AF27" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="AG27" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AH27" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AI27" s="12">
         <x:v>15</x:v>
@@ -3559,51 +3562,51 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="AK27" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AL27" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AM27" s="12">
         <x:v>15</x:v>
       </x:c>
       <x:c r="AN27" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AO27" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AP27" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AQ27" s="12">
         <x:v>15</x:v>
       </x:c>
       <x:c r="AR27" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AS27" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AT27" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AU27" s="12">
-        <x:v>29</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AV27" s="12" t="s">
-        <x:v>95</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="AW27" s="12">
-        <x:v>67</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="AX27" s="12" t="s">
-        <x:v>95</x:v>
+        <x:v>69</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:50">
       <x:c r="A28" s="11" t="s">
-        <x:v>97</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B28" s="12" t="s">
         <x:v>44</x:v>
@@ -3615,22 +3618,22 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="E28" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="F28" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="G28" s="12">
         <x:v>16</x:v>
       </x:c>
       <x:c r="H28" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="I28" s="12" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="J28" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="K28" s="12">
         <x:v>16</x:v>
@@ -3639,123 +3642,123 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="M28" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="N28" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="O28" s="12">
         <x:v>16</x:v>
       </x:c>
       <x:c r="P28" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="Q28" s="12" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="R28" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="S28" s="12">
         <x:v>16</x:v>
       </x:c>
       <x:c r="T28" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="U28" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="V28" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="W28" s="12">
         <x:v>16</x:v>
       </x:c>
       <x:c r="X28" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="Y28" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="Z28" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AA28" s="12">
         <x:v>16</x:v>
       </x:c>
       <x:c r="AB28" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AC28" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="AD28" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AE28" s="12">
         <x:v>16</x:v>
       </x:c>
       <x:c r="AF28" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AG28" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AH28" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AI28" s="12">
         <x:v>16</x:v>
       </x:c>
       <x:c r="AJ28" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AK28" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="AL28" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AM28" s="12">
         <x:v>16</x:v>
       </x:c>
       <x:c r="AN28" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AO28" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AP28" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AQ28" s="12">
         <x:v>16</x:v>
       </x:c>
       <x:c r="AR28" s="12" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="AS28" s="12" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="AS28" s="12" t="s">
+      <x:c r="AT28" s="12" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="AU28" s="12">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="AV28" s="12" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="AW28" s="12">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="AT28" s="12" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="AU28" s="12">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="AV28" s="12" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="AW28" s="12">
-        <x:v>49</x:v>
-      </x:c>
       <x:c r="AX28" s="12" t="s">
-        <x:v>98</x:v>
+        <x:v>87</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:50">
       <x:c r="A29" s="11" t="s">
-        <x:v>99</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B29" s="12" t="s">
         <x:v>44</x:v>
@@ -3767,22 +3770,22 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="E29" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="F29" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="G29" s="12">
         <x:v>17</x:v>
       </x:c>
       <x:c r="H29" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="I29" s="12" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="J29" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="K29" s="12">
         <x:v>17</x:v>
@@ -3791,70 +3794,70 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="M29" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="N29" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="O29" s="12">
         <x:v>17</x:v>
       </x:c>
       <x:c r="P29" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="Q29" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="R29" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="S29" s="12">
         <x:v>17</x:v>
       </x:c>
       <x:c r="T29" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="U29" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="V29" s="12" t="s">
-        <x:v>90</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="W29" s="12">
         <x:v>17</x:v>
       </x:c>
       <x:c r="X29" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="Y29" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="Z29" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AA29" s="12">
         <x:v>17</x:v>
       </x:c>
       <x:c r="AB29" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AC29" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AD29" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AE29" s="12">
         <x:v>17</x:v>
       </x:c>
       <x:c r="AF29" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AG29" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AH29" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AI29" s="12">
         <x:v>17</x:v>
@@ -3863,51 +3866,51 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="AK29" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AL29" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AM29" s="12">
         <x:v>17</x:v>
       </x:c>
       <x:c r="AN29" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AO29" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AP29" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AQ29" s="12">
         <x:v>17</x:v>
       </x:c>
       <x:c r="AR29" s="12" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="AS29" s="12" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="AS29" s="12" t="s">
+      <x:c r="AT29" s="12" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="AT29" s="12" t="s">
-        <x:v>53</x:v>
-      </x:c>
       <x:c r="AU29" s="12">
-        <x:v>52</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="AV29" s="12" t="s">
-        <x:v>100</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="AW29" s="12">
-        <x:v>73</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="AX29" s="12" t="s">
-        <x:v>68</x:v>
+        <x:v>69</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:50">
       <x:c r="A30" s="11" t="s">
-        <x:v>101</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="B30" s="12" t="s">
         <x:v>44</x:v>
@@ -3916,25 +3919,25 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="D30" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E30" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="F30" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="G30" s="12">
         <x:v>18</x:v>
       </x:c>
       <x:c r="H30" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="I30" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="J30" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="K30" s="12">
         <x:v>18</x:v>
@@ -3943,70 +3946,70 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="M30" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="N30" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="O30" s="12">
         <x:v>18</x:v>
       </x:c>
       <x:c r="P30" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="Q30" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="R30" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="S30" s="12">
         <x:v>18</x:v>
       </x:c>
       <x:c r="T30" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="U30" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="V30" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="W30" s="12">
         <x:v>18</x:v>
       </x:c>
       <x:c r="X30" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="Y30" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="Z30" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AA30" s="12">
         <x:v>18</x:v>
       </x:c>
       <x:c r="AB30" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AC30" s="12" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="AD30" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AE30" s="12">
         <x:v>18</x:v>
       </x:c>
       <x:c r="AF30" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AG30" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AH30" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AI30" s="12">
         <x:v>18</x:v>
@@ -4015,51 +4018,51 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="AK30" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AL30" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AM30" s="12">
         <x:v>18</x:v>
       </x:c>
       <x:c r="AN30" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AO30" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AP30" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AQ30" s="12">
         <x:v>18</x:v>
       </x:c>
       <x:c r="AR30" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AS30" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AT30" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AU30" s="12">
-        <x:v>20</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="AV30" s="12" t="s">
-        <x:v>66</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="AW30" s="12">
-        <x:v>28</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="AX30" s="12" t="s">
-        <x:v>82</x:v>
+        <x:v>63</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:50">
       <x:c r="A31" s="11" t="s">
-        <x:v>102</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B31" s="12" t="s">
         <x:v>44</x:v>
@@ -4068,25 +4071,25 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="D31" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E31" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="F31" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="G31" s="12">
         <x:v>19</x:v>
       </x:c>
       <x:c r="H31" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="I31" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="J31" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="K31" s="12">
         <x:v>19</x:v>
@@ -4095,123 +4098,123 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="M31" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="N31" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="O31" s="12">
         <x:v>19</x:v>
       </x:c>
       <x:c r="P31" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="Q31" s="12" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="R31" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="S31" s="12">
         <x:v>19</x:v>
       </x:c>
       <x:c r="T31" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="U31" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="V31" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="W31" s="12">
         <x:v>19</x:v>
       </x:c>
       <x:c r="X31" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="Y31" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="Z31" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AA31" s="12">
         <x:v>19</x:v>
       </x:c>
       <x:c r="AB31" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AC31" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AD31" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AE31" s="12">
         <x:v>19</x:v>
       </x:c>
       <x:c r="AF31" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AG31" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="AH31" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AI31" s="12">
         <x:v>19</x:v>
       </x:c>
       <x:c r="AJ31" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AK31" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="AL31" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AM31" s="12">
         <x:v>19</x:v>
       </x:c>
       <x:c r="AN31" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AO31" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AP31" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AQ31" s="12">
         <x:v>19</x:v>
       </x:c>
       <x:c r="AR31" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AS31" s="12" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="AT31" s="12" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="AT31" s="12" t="s">
-        <x:v>53</x:v>
-      </x:c>
       <x:c r="AU31" s="12">
-        <x:v>30</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="AV31" s="12" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="AW31" s="12">
-        <x:v>67</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="AX31" s="12" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:50">
       <x:c r="A32" s="11" t="s">
-        <x:v>103</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="B32" s="12" t="s">
         <x:v>44</x:v>
@@ -4223,22 +4226,22 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="E32" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="F32" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="G32" s="12">
         <x:v>20</x:v>
       </x:c>
       <x:c r="H32" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="I32" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="J32" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="K32" s="12">
         <x:v>20</x:v>
@@ -4247,123 +4250,123 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="M32" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="N32" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="O32" s="12">
         <x:v>20</x:v>
       </x:c>
       <x:c r="P32" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="Q32" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="R32" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="S32" s="12">
         <x:v>20</x:v>
       </x:c>
       <x:c r="T32" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="U32" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="V32" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="W32" s="12">
         <x:v>20</x:v>
       </x:c>
       <x:c r="X32" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="Y32" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="Z32" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AA32" s="12">
         <x:v>20</x:v>
       </x:c>
       <x:c r="AB32" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AC32" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AD32" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AE32" s="12">
         <x:v>20</x:v>
       </x:c>
       <x:c r="AF32" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AG32" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AH32" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AI32" s="12">
         <x:v>20</x:v>
       </x:c>
       <x:c r="AJ32" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AK32" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AL32" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AM32" s="12">
         <x:v>20</x:v>
       </x:c>
       <x:c r="AN32" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AO32" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AP32" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AQ32" s="12">
         <x:v>20</x:v>
       </x:c>
       <x:c r="AR32" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AS32" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AT32" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AU32" s="12">
-        <x:v>17</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="AV32" s="12" t="s">
-        <x:v>73</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="AW32" s="12">
-        <x:v>27</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AX32" s="12" t="s">
-        <x:v>82</x:v>
+        <x:v>75</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:50">
       <x:c r="A33" s="11" t="s">
-        <x:v>104</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="B33" s="12" t="s">
         <x:v>44</x:v>
@@ -4372,150 +4375,150 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D33" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E33" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="F33" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="G33" s="12">
         <x:v>21</x:v>
       </x:c>
       <x:c r="H33" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="I33" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="J33" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="K33" s="12">
         <x:v>21</x:v>
       </x:c>
       <x:c r="L33" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="M33" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="N33" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="O33" s="12">
         <x:v>21</x:v>
       </x:c>
       <x:c r="P33" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="Q33" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="R33" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="S33" s="12">
         <x:v>21</x:v>
       </x:c>
       <x:c r="T33" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="U33" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="V33" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="W33" s="12">
         <x:v>21</x:v>
       </x:c>
       <x:c r="X33" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="Y33" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="Z33" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AA33" s="12">
         <x:v>21</x:v>
       </x:c>
       <x:c r="AB33" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AC33" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AD33" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AE33" s="12">
         <x:v>21</x:v>
       </x:c>
       <x:c r="AF33" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AG33" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AH33" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AI33" s="12">
         <x:v>21</x:v>
       </x:c>
       <x:c r="AJ33" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AK33" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="AL33" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AM33" s="12">
         <x:v>21</x:v>
       </x:c>
       <x:c r="AN33" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AO33" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AP33" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AQ33" s="12">
         <x:v>21</x:v>
       </x:c>
       <x:c r="AR33" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AS33" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AT33" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AU33" s="12">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="AV33" s="12" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="AW33" s="12">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="AV33" s="12" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="AW33" s="12">
-        <x:v>18</x:v>
-      </x:c>
       <x:c r="AX33" s="12" t="s">
-        <x:v>88</x:v>
+        <x:v>90</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:50">
       <x:c r="A34" s="11" t="s">
-        <x:v>105</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B34" s="12" t="s">
         <x:v>44</x:v>
@@ -4527,22 +4530,22 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="E34" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="F34" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="G34" s="12">
         <x:v>22</x:v>
       </x:c>
       <x:c r="H34" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="I34" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="J34" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="K34" s="12">
         <x:v>22</x:v>
@@ -4554,67 +4557,67 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="N34" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="O34" s="12">
         <x:v>22</x:v>
       </x:c>
       <x:c r="P34" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="Q34" s="12" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="R34" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="S34" s="12">
         <x:v>22</x:v>
       </x:c>
       <x:c r="T34" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="U34" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="V34" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="W34" s="12">
         <x:v>22</x:v>
       </x:c>
       <x:c r="X34" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="Y34" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="Z34" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AA34" s="12">
         <x:v>22</x:v>
       </x:c>
       <x:c r="AB34" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AC34" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AD34" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AE34" s="12">
         <x:v>22</x:v>
       </x:c>
       <x:c r="AF34" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AG34" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AH34" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AI34" s="12">
         <x:v>22</x:v>
@@ -4623,51 +4626,51 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="AK34" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AL34" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AM34" s="12">
         <x:v>22</x:v>
       </x:c>
       <x:c r="AN34" s="12" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="AO34" s="12" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="AO34" s="12" t="s">
-        <x:v>49</x:v>
-      </x:c>
       <x:c r="AP34" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AQ34" s="12">
         <x:v>22</x:v>
       </x:c>
       <x:c r="AR34" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AS34" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AT34" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AU34" s="12">
-        <x:v>28</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AV34" s="12" t="s">
-        <x:v>65</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="AW34" s="12">
-        <x:v>39</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AX34" s="12" t="s">
-        <x:v>73</x:v>
+        <x:v>87</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:50">
       <x:c r="A35" s="11" t="s">
-        <x:v>106</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="B35" s="12" t="s">
         <x:v>44</x:v>
@@ -4676,25 +4679,25 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="D35" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E35" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="F35" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="G35" s="12">
         <x:v>23</x:v>
       </x:c>
       <x:c r="H35" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="I35" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="J35" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="K35" s="12">
         <x:v>23</x:v>
@@ -4703,70 +4706,70 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="M35" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="N35" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="O35" s="12">
         <x:v>23</x:v>
       </x:c>
       <x:c r="P35" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="Q35" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="R35" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="S35" s="12">
         <x:v>23</x:v>
       </x:c>
       <x:c r="T35" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="U35" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="V35" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="W35" s="12">
         <x:v>23</x:v>
       </x:c>
       <x:c r="X35" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="Y35" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="Z35" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AA35" s="12">
         <x:v>23</x:v>
       </x:c>
       <x:c r="AB35" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AC35" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AD35" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AE35" s="12">
         <x:v>23</x:v>
       </x:c>
       <x:c r="AF35" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AG35" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AH35" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AI35" s="12">
         <x:v>23</x:v>
@@ -4775,46 +4778,46 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="AK35" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AL35" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AM35" s="12">
         <x:v>23</x:v>
       </x:c>
       <x:c r="AN35" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AO35" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AP35" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AQ35" s="12">
         <x:v>23</x:v>
       </x:c>
       <x:c r="AR35" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AS35" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AT35" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AU35" s="12">
-        <x:v>40</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AV35" s="12" t="s">
-        <x:v>107</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="AW35" s="12">
-        <x:v>72</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="AX35" s="12" t="s">
-        <x:v>68</x:v>
+        <x:v>70</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:50">
@@ -4828,97 +4831,97 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="D36" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="E36" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="F36" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="G36" s="12">
         <x:v>24</x:v>
       </x:c>
       <x:c r="H36" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="I36" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="J36" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="K36" s="12">
         <x:v>24</x:v>
       </x:c>
       <x:c r="L36" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="M36" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="N36" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="O36" s="12">
         <x:v>24</x:v>
       </x:c>
       <x:c r="P36" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="Q36" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="R36" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="S36" s="12">
         <x:v>24</x:v>
       </x:c>
       <x:c r="T36" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="U36" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="V36" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="W36" s="12">
         <x:v>24</x:v>
       </x:c>
       <x:c r="X36" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="Y36" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="Z36" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AA36" s="12">
         <x:v>24</x:v>
       </x:c>
       <x:c r="AB36" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AC36" s="12" t="s">
         <x:v>109</x:v>
       </x:c>
       <x:c r="AD36" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AE36" s="12">
         <x:v>24</x:v>
       </x:c>
       <x:c r="AF36" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AG36" s="12" t="s">
         <x:v>109</x:v>
       </x:c>
       <x:c r="AH36" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AI36" s="12">
         <x:v>24</x:v>
@@ -4927,46 +4930,46 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="AK36" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AL36" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AM36" s="12">
         <x:v>24</x:v>
       </x:c>
       <x:c r="AN36" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AO36" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AP36" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AQ36" s="12">
         <x:v>24</x:v>
       </x:c>
       <x:c r="AR36" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AS36" s="12" t="s">
-        <x:v>90</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="AT36" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AU36" s="12">
-        <x:v>75</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="AV36" s="12" t="s">
-        <x:v>80</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="AW36" s="12">
-        <x:v>81</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="AX36" s="12" t="s">
-        <x:v>110</x:v>
+        <x:v>69</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:50">
@@ -4980,85 +4983,85 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="D37" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="E37" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="F37" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="G37" s="12">
         <x:v>25</x:v>
       </x:c>
       <x:c r="H37" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="I37" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="J37" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="K37" s="12">
         <x:v>25</x:v>
       </x:c>
       <x:c r="L37" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="M37" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="N37" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="O37" s="12">
         <x:v>25</x:v>
       </x:c>
       <x:c r="P37" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="Q37" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="R37" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="S37" s="12">
         <x:v>25</x:v>
       </x:c>
       <x:c r="T37" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="U37" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="V37" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="W37" s="12">
         <x:v>25</x:v>
       </x:c>
       <x:c r="X37" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="Y37" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="Z37" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AA37" s="12">
         <x:v>25</x:v>
       </x:c>
       <x:c r="AB37" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AC37" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AD37" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AE37" s="12">
         <x:v>25</x:v>
@@ -5067,10 +5070,10 @@
         <x:v>62</x:v>
       </x:c>
       <x:c r="AG37" s="12" t="s">
-        <x:v>112</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AH37" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AI37" s="12">
         <x:v>25</x:v>
@@ -5079,51 +5082,51 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="AK37" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AL37" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AM37" s="12">
         <x:v>25</x:v>
       </x:c>
       <x:c r="AN37" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AO37" s="12" t="s">
-        <x:v>113</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="AP37" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AQ37" s="12">
         <x:v>25</x:v>
       </x:c>
       <x:c r="AR37" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="AS37" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AT37" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AU37" s="12">
-        <x:v>80</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="AV37" s="12" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="AW37" s="12">
+        <x:v>232</x:v>
+      </x:c>
+      <x:c r="AX37" s="12" t="s">
         <x:v>114</x:v>
-      </x:c>
-      <x:c r="AW37" s="12">
-        <x:v>205</x:v>
-      </x:c>
-      <x:c r="AX37" s="12" t="s">
-        <x:v>115</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:50">
       <x:c r="A38" s="11" t="s">
-        <x:v>116</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B38" s="12" t="s">
         <x:v>44</x:v>
@@ -5132,25 +5135,25 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="D38" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E38" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="F38" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="G38" s="12">
         <x:v>26</x:v>
       </x:c>
       <x:c r="H38" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="I38" s="12" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="J38" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="K38" s="12">
         <x:v>26</x:v>
@@ -5162,67 +5165,67 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="N38" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="O38" s="12">
         <x:v>26</x:v>
       </x:c>
       <x:c r="P38" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="Q38" s="12" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="R38" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="S38" s="12">
         <x:v>26</x:v>
       </x:c>
       <x:c r="T38" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="U38" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="V38" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="W38" s="12">
         <x:v>26</x:v>
       </x:c>
       <x:c r="X38" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="Y38" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="Z38" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AA38" s="12">
         <x:v>26</x:v>
       </x:c>
       <x:c r="AB38" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AC38" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="AD38" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AE38" s="12">
         <x:v>26</x:v>
       </x:c>
       <x:c r="AF38" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AG38" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AH38" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AI38" s="12">
         <x:v>26</x:v>
@@ -5231,198 +5234,198 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="AK38" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="AL38" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AM38" s="12">
         <x:v>26</x:v>
       </x:c>
       <x:c r="AN38" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AO38" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AP38" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AQ38" s="12">
         <x:v>26</x:v>
       </x:c>
       <x:c r="AR38" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AS38" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AT38" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AU38" s="12">
-        <x:v>33</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AV38" s="12" t="s">
-        <x:v>68</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="AW38" s="12">
-        <x:v>78</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="AX38" s="12" t="s">
-        <x:v>110</x:v>
+        <x:v>66</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:50">
       <x:c r="A39" s="11" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="B39" s="12" t="s">
         <x:v>117</x:v>
-      </x:c>
-      <x:c r="B39" s="12" t="s">
-        <x:v>118</x:v>
       </x:c>
       <x:c r="C39" s="12">
         <x:v>27</x:v>
       </x:c>
       <x:c r="D39" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="E39" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="F39" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="G39" s="12">
         <x:v>27</x:v>
       </x:c>
       <x:c r="H39" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="I39" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="J39" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="K39" s="12">
         <x:v>27</x:v>
       </x:c>
       <x:c r="L39" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="M39" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="N39" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="O39" s="12">
         <x:v>27</x:v>
       </x:c>
       <x:c r="P39" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="Q39" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="R39" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="S39" s="12">
         <x:v>27</x:v>
       </x:c>
       <x:c r="T39" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="U39" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="V39" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="W39" s="12">
         <x:v>27</x:v>
       </x:c>
       <x:c r="X39" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="Y39" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="Z39" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AA39" s="12">
         <x:v>27</x:v>
       </x:c>
       <x:c r="AB39" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="AC39" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AD39" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AE39" s="12">
         <x:v>27</x:v>
       </x:c>
       <x:c r="AF39" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="AG39" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AH39" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AI39" s="12">
         <x:v>27</x:v>
       </x:c>
       <x:c r="AJ39" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="AK39" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AL39" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AM39" s="12">
         <x:v>27</x:v>
       </x:c>
       <x:c r="AN39" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="AO39" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AP39" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AQ39" s="12">
         <x:v>27</x:v>
       </x:c>
       <x:c r="AR39" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="AS39" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AT39" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AU39" s="12">
         <x:v>0</x:v>
       </x:c>
       <x:c r="AV39" s="12" t="s">
-        <x:v>79</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="AW39" s="12">
         <x:v>131</x:v>
       </x:c>
       <x:c r="AX39" s="12" t="s">
-        <x:v>91</x:v>
+        <x:v>118</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:50">
@@ -5436,25 +5439,25 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="D40" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E40" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="F40" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="G40" s="12">
         <x:v>28</x:v>
       </x:c>
       <x:c r="H40" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="I40" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="J40" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="K40" s="12">
         <x:v>28</x:v>
@@ -5463,70 +5466,70 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="M40" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="N40" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="O40" s="12">
         <x:v>28</x:v>
       </x:c>
       <x:c r="P40" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="Q40" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="R40" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="S40" s="12">
         <x:v>28</x:v>
       </x:c>
       <x:c r="T40" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="U40" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="V40" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="W40" s="12">
         <x:v>28</x:v>
       </x:c>
       <x:c r="X40" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="Y40" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="Z40" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AA40" s="12">
         <x:v>28</x:v>
       </x:c>
       <x:c r="AB40" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AC40" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AD40" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AE40" s="12">
         <x:v>28</x:v>
       </x:c>
       <x:c r="AF40" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AG40" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AH40" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AI40" s="12">
         <x:v>28</x:v>
@@ -5535,34 +5538,34 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="AK40" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AL40" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AM40" s="12">
         <x:v>28</x:v>
       </x:c>
       <x:c r="AN40" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AO40" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="AP40" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AQ40" s="12">
         <x:v>28</x:v>
       </x:c>
       <x:c r="AR40" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AS40" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AT40" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AU40" s="12">
         <x:v>2</x:v>
@@ -5591,22 +5594,22 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="E41" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="F41" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="G41" s="12">
         <x:v>29</x:v>
       </x:c>
       <x:c r="H41" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="I41" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="J41" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="K41" s="12">
         <x:v>29</x:v>
@@ -5615,70 +5618,70 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="M41" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="N41" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="O41" s="12">
         <x:v>29</x:v>
       </x:c>
       <x:c r="P41" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="Q41" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="R41" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="S41" s="12">
         <x:v>29</x:v>
       </x:c>
       <x:c r="T41" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="U41" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="V41" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="W41" s="12">
         <x:v>29</x:v>
       </x:c>
       <x:c r="X41" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="Y41" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="Z41" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AA41" s="12">
         <x:v>29</x:v>
       </x:c>
       <x:c r="AB41" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AC41" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AD41" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AE41" s="12">
         <x:v>29</x:v>
       </x:c>
       <x:c r="AF41" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AG41" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AH41" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AI41" s="12">
         <x:v>29</x:v>
@@ -5687,34 +5690,34 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="AK41" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AL41" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AM41" s="12">
         <x:v>29</x:v>
       </x:c>
       <x:c r="AN41" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AO41" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="AP41" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AQ41" s="12">
         <x:v>29</x:v>
       </x:c>
       <x:c r="AR41" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AS41" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AT41" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AU41" s="12">
         <x:v>2</x:v>
@@ -5740,97 +5743,97 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="D42" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E42" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="F42" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="G42" s="12">
         <x:v>30</x:v>
       </x:c>
       <x:c r="H42" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="I42" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="J42" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="K42" s="12">
         <x:v>30</x:v>
       </x:c>
       <x:c r="L42" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="M42" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="N42" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="O42" s="12">
         <x:v>30</x:v>
       </x:c>
       <x:c r="P42" s="12" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="Q42" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="Q42" s="12" t="s">
-        <x:v>47</x:v>
-      </x:c>
       <x:c r="R42" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="S42" s="12">
         <x:v>30</x:v>
       </x:c>
       <x:c r="T42" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="U42" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="V42" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="W42" s="12">
         <x:v>30</x:v>
       </x:c>
       <x:c r="X42" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="Y42" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="Z42" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AA42" s="12">
         <x:v>30</x:v>
       </x:c>
       <x:c r="AB42" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AC42" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AD42" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AE42" s="12">
         <x:v>30</x:v>
       </x:c>
       <x:c r="AF42" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AG42" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AH42" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AI42" s="12">
         <x:v>30</x:v>
@@ -5839,51 +5842,51 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="AK42" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AL42" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AM42" s="12">
         <x:v>30</x:v>
       </x:c>
       <x:c r="AN42" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AO42" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AP42" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AQ42" s="12">
         <x:v>30</x:v>
       </x:c>
       <x:c r="AR42" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AS42" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AT42" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AU42" s="12">
-        <x:v>47</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="AV42" s="12" t="s">
         <x:v>123</x:v>
       </x:c>
       <x:c r="AW42" s="12">
-        <x:v>104</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="AX42" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>124</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:50">
       <x:c r="A43" s="11" t="s">
-        <x:v>124</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="B43" s="12" t="s">
         <x:v>44</x:v>
@@ -5892,150 +5895,150 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="D43" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="E43" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="F43" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="G43" s="12">
         <x:v>31</x:v>
       </x:c>
       <x:c r="H43" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="I43" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="J43" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="K43" s="12">
         <x:v>31</x:v>
       </x:c>
       <x:c r="L43" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="M43" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="N43" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="O43" s="12">
         <x:v>31</x:v>
       </x:c>
       <x:c r="P43" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="Q43" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="R43" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="S43" s="12">
         <x:v>31</x:v>
       </x:c>
       <x:c r="T43" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="U43" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="V43" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="W43" s="12">
         <x:v>31</x:v>
       </x:c>
       <x:c r="X43" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="Y43" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="Z43" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AA43" s="12">
         <x:v>31</x:v>
       </x:c>
       <x:c r="AB43" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AC43" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AD43" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AE43" s="12">
         <x:v>31</x:v>
       </x:c>
       <x:c r="AF43" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AG43" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AH43" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AI43" s="12">
         <x:v>31</x:v>
       </x:c>
       <x:c r="AJ43" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AK43" s="12" t="s">
         <x:v>45</x:v>
       </x:c>
       <x:c r="AL43" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AM43" s="12">
         <x:v>31</x:v>
       </x:c>
       <x:c r="AN43" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AO43" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AP43" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AQ43" s="12">
         <x:v>31</x:v>
       </x:c>
       <x:c r="AR43" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="AS43" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AT43" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AU43" s="12">
-        <x:v>38</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AV43" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="AW43" s="12">
-        <x:v>54</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="AX43" s="12" t="s">
-        <x:v>98</x:v>
+        <x:v>67</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:50">
       <x:c r="A44" s="11" t="s">
-        <x:v>125</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="B44" s="12" t="s">
         <x:v>44</x:v>
@@ -6044,25 +6047,25 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="D44" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E44" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="F44" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="G44" s="12">
         <x:v>32</x:v>
       </x:c>
       <x:c r="H44" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="I44" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="J44" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="K44" s="12">
         <x:v>32</x:v>
@@ -6071,70 +6074,70 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="M44" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="N44" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="O44" s="12">
         <x:v>32</x:v>
       </x:c>
       <x:c r="P44" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="Q44" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="R44" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="S44" s="12">
         <x:v>32</x:v>
       </x:c>
       <x:c r="T44" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="U44" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="V44" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="W44" s="12">
         <x:v>32</x:v>
       </x:c>
       <x:c r="X44" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="Y44" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="Z44" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AA44" s="12">
         <x:v>32</x:v>
       </x:c>
       <x:c r="AB44" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AC44" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AD44" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AE44" s="12">
         <x:v>32</x:v>
       </x:c>
       <x:c r="AF44" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AG44" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AH44" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AI44" s="12">
         <x:v>32</x:v>
@@ -6143,51 +6146,51 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="AK44" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AL44" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AM44" s="12">
         <x:v>32</x:v>
       </x:c>
       <x:c r="AN44" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AO44" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AP44" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AQ44" s="12">
         <x:v>32</x:v>
       </x:c>
       <x:c r="AR44" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AS44" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AT44" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AU44" s="12">
-        <x:v>40</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AV44" s="12" t="s">
-        <x:v>107</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="AW44" s="12">
-        <x:v>78</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="AX44" s="12" t="s">
-        <x:v>110</x:v>
+        <x:v>70</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:50">
       <x:c r="A45" s="11" t="s">
-        <x:v>126</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="B45" s="12" t="s">
         <x:v>44</x:v>
@@ -6196,85 +6199,85 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="D45" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="E45" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="F45" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="G45" s="12">
         <x:v>33</x:v>
       </x:c>
       <x:c r="H45" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="I45" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="J45" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="K45" s="12">
         <x:v>33</x:v>
       </x:c>
       <x:c r="L45" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="M45" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="N45" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="O45" s="12">
         <x:v>33</x:v>
       </x:c>
       <x:c r="P45" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="Q45" s="12" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="R45" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="S45" s="12">
         <x:v>33</x:v>
       </x:c>
       <x:c r="T45" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="U45" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="V45" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="W45" s="12">
         <x:v>33</x:v>
       </x:c>
       <x:c r="X45" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="Y45" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="Z45" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AA45" s="12">
         <x:v>33</x:v>
       </x:c>
       <x:c r="AB45" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AC45" s="12" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="AD45" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AE45" s="12">
         <x:v>33</x:v>
@@ -6283,63 +6286,63 @@
         <x:v>62</x:v>
       </x:c>
       <x:c r="AG45" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AH45" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AI45" s="12">
         <x:v>33</x:v>
       </x:c>
       <x:c r="AJ45" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AK45" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AL45" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AM45" s="12">
         <x:v>33</x:v>
       </x:c>
       <x:c r="AN45" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AO45" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AP45" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AQ45" s="12">
         <x:v>33</x:v>
       </x:c>
       <x:c r="AR45" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="AS45" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AT45" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AU45" s="12">
-        <x:v>20</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="AV45" s="12" t="s">
-        <x:v>66</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="AW45" s="12">
-        <x:v>40</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AX45" s="12" t="s">
-        <x:v>73</x:v>
+        <x:v>75</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:50">
       <x:c r="A46" s="11" t="s">
-        <x:v>127</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="B46" s="12" t="s">
         <x:v>44</x:v>
@@ -6351,22 +6354,22 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="E46" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="F46" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="G46" s="12">
         <x:v>34</x:v>
       </x:c>
       <x:c r="H46" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="I46" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="J46" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="K46" s="12">
         <x:v>34</x:v>
@@ -6375,70 +6378,70 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="M46" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="N46" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="O46" s="12">
         <x:v>34</x:v>
       </x:c>
       <x:c r="P46" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="Q46" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="R46" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="S46" s="12">
         <x:v>34</x:v>
       </x:c>
       <x:c r="T46" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="U46" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="V46" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="W46" s="12">
         <x:v>34</x:v>
       </x:c>
       <x:c r="X46" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="Y46" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="Z46" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AA46" s="12">
         <x:v>34</x:v>
       </x:c>
       <x:c r="AB46" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AC46" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="AD46" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AE46" s="12">
         <x:v>34</x:v>
       </x:c>
       <x:c r="AF46" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AG46" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AH46" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AI46" s="12">
         <x:v>34</x:v>
@@ -6447,51 +6450,51 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="AK46" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AL46" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AM46" s="12">
         <x:v>34</x:v>
       </x:c>
       <x:c r="AN46" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AO46" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="AP46" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AQ46" s="12">
         <x:v>34</x:v>
       </x:c>
       <x:c r="AR46" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AS46" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AT46" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AU46" s="12">
-        <x:v>13</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="AV46" s="12" t="s">
-        <x:v>82</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="AW46" s="12">
-        <x:v>29</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="AX46" s="12" t="s">
-        <x:v>82</x:v>
+        <x:v>63</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:50">
       <x:c r="A47" s="11" t="s">
-        <x:v>128</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="B47" s="12" t="s">
         <x:v>44</x:v>
@@ -6500,97 +6503,97 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D47" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="E47" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="F47" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="G47" s="12">
         <x:v>35</x:v>
       </x:c>
       <x:c r="H47" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="I47" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="J47" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="K47" s="12">
         <x:v>35</x:v>
       </x:c>
       <x:c r="L47" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="M47" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="N47" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="O47" s="12">
         <x:v>35</x:v>
       </x:c>
       <x:c r="P47" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="Q47" s="12" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="R47" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="S47" s="12">
         <x:v>35</x:v>
       </x:c>
       <x:c r="T47" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="U47" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="V47" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="W47" s="12">
         <x:v>35</x:v>
       </x:c>
       <x:c r="X47" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="Y47" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="Z47" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AA47" s="12">
         <x:v>35</x:v>
       </x:c>
       <x:c r="AB47" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AC47" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AD47" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AE47" s="12">
         <x:v>35</x:v>
       </x:c>
       <x:c r="AF47" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="AG47" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AH47" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AI47" s="12">
         <x:v>35</x:v>
@@ -6599,46 +6602,46 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="AK47" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AL47" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AM47" s="12">
         <x:v>35</x:v>
       </x:c>
       <x:c r="AN47" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AO47" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AP47" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AQ47" s="12">
         <x:v>35</x:v>
       </x:c>
       <x:c r="AR47" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="AS47" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AT47" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AU47" s="12">
-        <x:v>52</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="AV47" s="12" t="s">
-        <x:v>100</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="AW47" s="12">
-        <x:v>143</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="AX47" s="12" t="s">
-        <x:v>129</x:v>
+        <x:v>57</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:50">
@@ -6655,94 +6658,94 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="E48" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="F48" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="G48" s="12">
         <x:v>36</x:v>
       </x:c>
       <x:c r="H48" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="I48" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="J48" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="K48" s="12">
         <x:v>36</x:v>
       </x:c>
       <x:c r="L48" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="M48" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="N48" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="O48" s="12">
         <x:v>36</x:v>
       </x:c>
       <x:c r="P48" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="Q48" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="R48" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="S48" s="12">
         <x:v>36</x:v>
       </x:c>
       <x:c r="T48" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="U48" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="V48" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="W48" s="12">
         <x:v>36</x:v>
       </x:c>
       <x:c r="X48" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="Y48" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="Z48" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AA48" s="12">
         <x:v>36</x:v>
       </x:c>
       <x:c r="AB48" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AC48" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AD48" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AE48" s="12">
         <x:v>36</x:v>
       </x:c>
       <x:c r="AF48" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AG48" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AH48" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AI48" s="12">
         <x:v>36</x:v>
@@ -6751,51 +6754,51 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="AK48" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AL48" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AM48" s="12">
         <x:v>36</x:v>
       </x:c>
       <x:c r="AN48" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AO48" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AP48" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AQ48" s="12">
         <x:v>36</x:v>
       </x:c>
       <x:c r="AR48" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AS48" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AT48" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AU48" s="12">
-        <x:v>17</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="AV48" s="12" t="s">
-        <x:v>73</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="AW48" s="12">
-        <x:v>33</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="AX48" s="12" t="s">
-        <x:v>131</x:v>
+        <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:50">
       <x:c r="A49" s="11" t="s">
-        <x:v>132</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="B49" s="12" t="s">
         <x:v>44</x:v>
@@ -6807,22 +6810,22 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="E49" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="F49" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="G49" s="12">
         <x:v>37</x:v>
       </x:c>
       <x:c r="H49" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="I49" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="J49" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="K49" s="12">
         <x:v>37</x:v>
@@ -6831,70 +6834,70 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="M49" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="N49" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="O49" s="12">
         <x:v>37</x:v>
       </x:c>
       <x:c r="P49" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="Q49" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="R49" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="S49" s="12">
         <x:v>37</x:v>
       </x:c>
       <x:c r="T49" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="U49" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="V49" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="W49" s="12">
         <x:v>37</x:v>
       </x:c>
       <x:c r="X49" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="Y49" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="Z49" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AA49" s="12">
         <x:v>37</x:v>
       </x:c>
       <x:c r="AB49" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AC49" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AD49" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AE49" s="12">
         <x:v>37</x:v>
       </x:c>
       <x:c r="AF49" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AG49" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AH49" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AI49" s="12">
         <x:v>37</x:v>
@@ -6903,46 +6906,46 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="AK49" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AL49" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AM49" s="12">
         <x:v>37</x:v>
       </x:c>
       <x:c r="AN49" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AO49" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AP49" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AQ49" s="12">
         <x:v>37</x:v>
       </x:c>
       <x:c r="AR49" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AS49" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AT49" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AU49" s="12">
-        <x:v>0</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AV49" s="12" t="s">
-        <x:v>79</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="AW49" s="12">
-        <x:v>8</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="AX49" s="12" t="s">
-        <x:v>120</x:v>
+        <x:v>132</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:50">
@@ -7001,19 +7004,19 @@
       <x:c r="AG50" s="7"/>
       <x:c r="AH50" s="7"/>
       <x:c r="AI50" s="7" t="s">
-        <x:v>134</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="AJ50" s="7"/>
       <x:c r="AK50" s="7"/>
       <x:c r="AL50" s="7"/>
       <x:c r="AM50" s="7" t="s">
-        <x:v>139</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="AN50" s="7"/>
       <x:c r="AO50" s="7"/>
       <x:c r="AP50" s="7"/>
       <x:c r="AQ50" s="7" t="s">
-        <x:v>140</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="AR50" s="7"/>
       <x:c r="AS50" s="7"/>
@@ -7025,37 +7028,37 @@
     </x:row>
     <x:row r="52" spans="1:50">
       <x:c r="A52" s="14" t="s">
-        <x:v>141</x:v>
+        <x:v>142</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:50">
       <x:c r="A53" s="13" t="s">
-        <x:v>142</x:v>
+        <x:v>143</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:50">
       <x:c r="A54" s="13" t="s">
-        <x:v>143</x:v>
+        <x:v>144</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:50">
       <x:c r="A55" s="13" t="s">
-        <x:v>144</x:v>
+        <x:v>145</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:50">
       <x:c r="A56" s="13" t="s">
-        <x:v>145</x:v>
+        <x:v>146</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:50">
       <x:c r="A57" s="13" t="s">
-        <x:v>146</x:v>
+        <x:v>147</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:50">
       <x:c r="A58" s="13" t="s">
-        <x:v>147</x:v>
+        <x:v>148</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
